--- a/data/mock/jd_product_202610.xlsx
+++ b/data/mock/jd_product_202610.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>360</v>
       </c>
       <c r="F2" t="n">
-        <v>1349</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="3">
@@ -494,14 +494,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>￥89.00</t>
+          <t>￥69.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>385</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>1297</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>354</v>
       </c>
       <c r="F4" t="n">
-        <v>1436</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="5">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="F5" t="n">
-        <v>760</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="F6" t="n">
-        <v>707</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7">
@@ -606,14 +606,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>￥529.00</t>
+          <t>￥599.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>390</v>
+        <v>168</v>
       </c>
       <c r="F7" t="n">
-        <v>879</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>328</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>1384</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="9">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="F9" t="n">
-        <v>1400</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -690,14 +690,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>￥95.00</t>
+          <t>￥79.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>345</v>
+        <v>56</v>
       </c>
       <c r="F10" t="n">
-        <v>743</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="F11" t="n">
-        <v>188</v>
+        <v>679</v>
       </c>
     </row>
     <row r="12">
@@ -746,14 +746,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>￥349.00</t>
+          <t>￥399.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>571</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="13">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>298</v>
+        <v>204</v>
       </c>
       <c r="F13" t="n">
-        <v>1112</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106</v>
+        <v>381</v>
       </c>
       <c r="F14" t="n">
-        <v>1135</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164</v>
+        <v>292</v>
       </c>
       <c r="F15" t="n">
-        <v>899</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="16">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="F16" t="n">
-        <v>1136</v>
+        <v>922</v>
       </c>
     </row>
     <row r="17">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>79</v>
+        <v>254</v>
       </c>
       <c r="F17" t="n">
-        <v>970</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>337</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>134</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="19">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>314</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>1079</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="20">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>398</v>
       </c>
       <c r="F20" t="n">
-        <v>1383</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="21">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>239</v>
+        <v>121</v>
       </c>
       <c r="F21" t="n">
-        <v>256</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="F22" t="n">
-        <v>689</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>63</v>
+        <v>374</v>
       </c>
       <c r="F23" t="n">
-        <v>957</v>
+        <v>767</v>
       </c>
     </row>
     <row r="24">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="F24" t="n">
-        <v>1239</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="25">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>197</v>
+        <v>159</v>
       </c>
       <c r="F25" t="n">
-        <v>1364</v>
+        <v>638</v>
       </c>
     </row>
     <row r="26">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F26" t="n">
-        <v>401</v>
+        <v>799</v>
       </c>
     </row>
   </sheetData>

--- a/data/mock/jd_product_202610.xlsx
+++ b/data/mock/jd_product_202610.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>360</v>
+        <v>124</v>
       </c>
       <c r="F2" t="n">
-        <v>1363</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="F3" t="n">
-        <v>1100</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="F4" t="n">
-        <v>1169</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="5">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>194</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>399</v>
+        <v>885</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>187</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>398</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>168</v>
+        <v>256</v>
       </c>
       <c r="F7" t="n">
-        <v>522</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="8">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>399</v>
       </c>
       <c r="F8" t="n">
-        <v>1114</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="9">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>108</v>
+        <v>260</v>
       </c>
       <c r="F9" t="n">
-        <v>128</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="10">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="F10" t="n">
-        <v>643</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="F11" t="n">
-        <v>679</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="12">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>310</v>
       </c>
       <c r="F12" t="n">
-        <v>1017</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F13" t="n">
-        <v>400</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="14">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>381</v>
+        <v>251</v>
       </c>
       <c r="F14" t="n">
-        <v>298</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="F15" t="n">
-        <v>1024</v>
+        <v>738</v>
       </c>
     </row>
     <row r="16">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>348</v>
+        <v>170</v>
       </c>
       <c r="F16" t="n">
-        <v>922</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="F17" t="n">
-        <v>428</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="18">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>177</v>
       </c>
       <c r="F18" t="n">
-        <v>1254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="F19" t="n">
-        <v>1253</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>398</v>
+        <v>250</v>
       </c>
       <c r="F20" t="n">
-        <v>1354</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="21">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="F21" t="n">
-        <v>201</v>
+        <v>924</v>
       </c>
     </row>
     <row r="22">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="F22" t="n">
-        <v>312</v>
+        <v>542</v>
       </c>
     </row>
     <row r="23">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>374</v>
+        <v>126</v>
       </c>
       <c r="F23" t="n">
-        <v>767</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="24">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="F24" t="n">
-        <v>1144</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="25">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="F25" t="n">
-        <v>638</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F26" t="n">
-        <v>799</v>
+        <v>1054</v>
       </c>
     </row>
   </sheetData>
